--- a/HumanBartender/outputs/20260915-content-editing/HumanBartender_C_Content.xlsx
+++ b/HumanBartender/outputs/20260915-content-editing/HumanBartender_C_Content.xlsx
@@ -2,29 +2,29 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Index" sheetId="1" r:id="R63f62f7cb57c4c34"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SourceInventory" sheetId="2" r:id="R3a654eb4bc41490c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ScriptFiles" sheetId="3" r:id="Rac8ce2dc62a4475d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Scenes" sheetId="4" r:id="Rede8dde8e8994025"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Steps" sheetId="5" r:id="Rdeea6678f5d54ee5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BarChoiceGroups" sheetId="6" r:id="Rc51b35b1cb054579"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BarChoices" sheetId="7" r:id="Rb563dba9e0eb4ea1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="StreetChoices" sheetId="8" r:id="R33e23de49d7a439f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="InteractPoints" sheetId="9" r:id="R1d330cf50c234420"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DialogueFlows" sheetId="10" r:id="Rce32d2b9aa054d42"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Characters" sheetId="11" r:id="R567a9b98e5f94f76"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CharacterExpressions" sheetId="12" r:id="R2c489ab2a5ae409b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AnimationCharacters" sheetId="13" r:id="Rfcf0f0cd4c7c4865"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Expressions" sheetId="14" r:id="R7b8f6c1fe93545e7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ExpressionParts" sheetId="15" r:id="Ra510928112c64fb3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cutscenes" sheetId="16" r:id="R4916b5e81279497c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FieldAnimations" sheetId="17" r:id="R026fe28444954c8d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Spots" sheetId="18" r:id="R10527eb94ec4465c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TextTags" sheetId="19" r:id="Ra2c9343e07f94911"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dossier" sheetId="20" r:id="R31ba24af1b104139"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FieldGuide" sheetId="21" r:id="Re44ec271c2c94ff4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="StepTypes" sheetId="22" r:id="R7dc7accdd1174ec8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ReadMe" sheetId="23" r:id="R64efcd7881a94a71"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Index" sheetId="1" r:id="R2d02c8778e6b4d1c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SourceInventory" sheetId="2" r:id="R7aa197b8152147e4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ScriptFiles" sheetId="3" r:id="Ra4682b50a0b148c0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Scenes" sheetId="4" r:id="R86a2495b5a41422f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Steps" sheetId="5" r:id="R6022f6b24f5e4ef2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BarChoiceGroups" sheetId="6" r:id="R1920eaad35524d88"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BarChoices" sheetId="7" r:id="R656a2cf803f74efc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="StreetChoices" sheetId="8" r:id="Rd82cd9cc601e4174"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="InteractPoints" sheetId="9" r:id="Re8fdda4fc0514f91"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DialogueFlows" sheetId="10" r:id="R29cb44e427904dfd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Characters" sheetId="11" r:id="R48e631238b324110"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CharacterExpressions" sheetId="12" r:id="R943c677b14c84b24"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AnimationCharacters" sheetId="13" r:id="R48f93660e3db4103"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Expressions" sheetId="14" r:id="Re1eaabcc6e6c4bb7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ExpressionParts" sheetId="15" r:id="R06920f67e4bb404b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cutscenes" sheetId="16" r:id="Re8b0ff7fc3b64038"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FieldAnimations" sheetId="17" r:id="R944e47d58339483a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Spots" sheetId="18" r:id="R410166b6498343f6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TextTags" sheetId="19" r:id="Rb96d81c27cdf4519"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dossier" sheetId="20" r:id="R501a4e8af1854446"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FieldGuide" sheetId="21" r:id="R5b2189c535054d4f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="StepTypes" sheetId="22" r:id="R4d006ba1a29d42a4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ReadMe" sheetId="23" r:id="Rb497c00603fd47e2"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -67,7 +67,7 @@
       <x:name val="Arial Unicode MS"/>
     </x:font>
   </x:fonts>
-  <x:fills count="5">
+  <x:fills count="7">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -89,6 +89,16 @@
         <x:fgColor rgb="FFEDF1F5"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFF6DE"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFEDF2F7"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
   <x:borders count="2">
     <x:border/>
@@ -101,7 +111,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="30">
+  <x:cellXfs count="32">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -208,6 +218,8 @@
         </x:ext>
       </x:extLst>
     </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -218,7 +230,7 @@
         <x:color rgb="FF9B560E"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFFF0D1"/>
         </x:patternFill>
       </x:fill>
@@ -228,7 +240,7 @@
         <x:color rgb="FFB52222"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFCE2E2"/>
         </x:patternFill>
       </x:fill>
@@ -238,7 +250,7 @@
         <x:color rgb="FFB52222"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFCE2E2"/>
         </x:patternFill>
       </x:fill>
@@ -248,7 +260,7 @@
         <x:color rgb="FFB52222"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFCE2E2"/>
         </x:patternFill>
       </x:fill>
@@ -258,7 +270,7 @@
         <x:color rgb="FFB52222"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFCE2E2"/>
         </x:patternFill>
       </x:fill>
@@ -268,7 +280,7 @@
         <x:color rgb="FFB52222"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFCE2E2"/>
         </x:patternFill>
       </x:fill>
@@ -278,7 +290,7 @@
         <x:color rgb="FFB52222"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFCE2E2"/>
         </x:patternFill>
       </x:fill>
@@ -288,7 +300,7 @@
         <x:color rgb="FFB52222"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFCE2E2"/>
         </x:patternFill>
       </x:fill>
@@ -298,7 +310,7 @@
         <x:color rgb="FFB52222"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFCE2E2"/>
         </x:patternFill>
       </x:fill>
@@ -308,7 +320,7 @@
         <x:color rgb="FFB52222"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFCE2E2"/>
         </x:patternFill>
       </x:fill>
@@ -318,7 +330,7 @@
         <x:color rgb="FFB52222"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFCE2E2"/>
         </x:patternFill>
       </x:fill>
@@ -328,7 +340,7 @@
         <x:color rgb="FFB52222"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFCE2E2"/>
         </x:patternFill>
       </x:fill>
@@ -338,7 +350,7 @@
         <x:color rgb="FFB52222"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFCE2E2"/>
         </x:patternFill>
       </x:fill>
@@ -348,7 +360,7 @@
         <x:color rgb="FFB52222"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFCE2E2"/>
         </x:patternFill>
       </x:fill>
@@ -358,7 +370,7 @@
         <x:color rgb="FFB52222"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFCE2E2"/>
         </x:patternFill>
       </x:fill>
@@ -368,7 +380,7 @@
         <x:color rgb="FFB52222"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFCE2E2"/>
         </x:patternFill>
       </x:fill>
@@ -378,7 +390,7 @@
         <x:color rgb="FFB52222"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFCE2E2"/>
         </x:patternFill>
       </x:fill>
@@ -388,7 +400,7 @@
         <x:color rgb="FFB52222"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFCE2E2"/>
         </x:patternFill>
       </x:fill>
@@ -398,7 +410,7 @@
         <x:color rgb="FFB52222"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFCE2E2"/>
         </x:patternFill>
       </x:fill>
@@ -660,8 +672,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="C_Scenes" displayName="C_Scenes" ref="A5:O69" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A5:O69"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="C_Scenes" displayName="C_Scenes" ref="A5:O70" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A5:O70"/>
   <x:tableColumns count="15">
     <x:tableColumn id="1" name="id"/>
     <x:tableColumn id="2" name="day"/>
@@ -684,8 +696,8 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="C_Steps" displayName="C_Steps" ref="A5:R670" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A5:R670"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="C_Steps" displayName="C_Steps" ref="A5:R673" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A5:R673"/>
   <x:tableColumns count="18">
     <x:tableColumn id="1" name="context"/>
     <x:tableColumn id="2" name="seq"/>
@@ -1092,7 +1104,7 @@
       </x:c>
       <x:c r="C7" s="2" t="n">
         <x:f>COUNTA('Scenes'!$K$6:$K$1069)</x:f>
-        <x:v>64</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="D7" s="2" t="str">
         <x:v>story/scenes.csv</x:v>
@@ -1107,7 +1119,7 @@
       </x:c>
       <x:c r="C8" s="2" t="n">
         <x:f>COUNTA('Steps'!$N$6:$N$1670)</x:f>
-        <x:v>665</x:v>
+        <x:v>668</x:v>
       </x:c>
       <x:c r="D8" s="2" t="str">
         <x:v>story/steps.csv</x:v>
@@ -2186,7 +2198,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re7462bd92dfc4602"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Red768813958a413b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3261,7 +3273,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb54b0fed9836424d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1e2d547b947043ed"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4298,7 +4310,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R68eca834391f4c71"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1ffe5a94c5214dbf"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5168,7 +5180,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8949ebc6050649ac"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R59065372d4ce4194"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8098,7 +8110,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8c54022fad6f4800"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R76d0653bc8c84fbd"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11226,7 +11238,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R485be002e88e43f7"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re262c3f04fa843d5"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11369,7 +11381,7 @@
         <x:v>timeline</x:v>
       </x:c>
       <x:c r="C7" s="18" t="str">
-        <x:v>Intro lab</x:v>
+        <x:v>Intro_lab</x:v>
       </x:c>
       <x:c r="D7" s="18" t="str">
         <x:v>연구소 도입 — 꿈(습격) 연출 재료</x:v>
@@ -11429,7 +11441,7 @@
         <x:v>timeline</x:v>
       </x:c>
       <x:c r="C9" s="18" t="str">
-        <x:v>Bubi_meet</x:v>
+        <x:v>day1_bubi_fetch</x:v>
       </x:c>
       <x:c r="D9" s="18" t="str">
         <x:v>부비 첫 만남 — d3_aili_bubi 승격 후보</x:v>
@@ -11459,7 +11471,7 @@
         <x:v>timeline</x:v>
       </x:c>
       <x:c r="C10" s="18" t="str">
-        <x:v>Catmilk</x:v>
+        <x:v>day1_bubi_drink_reaction</x:v>
       </x:c>
       <x:c r="D10" s="18" t="str">
         <x:v>깔루아밀크 × 고양이 연출</x:v>
@@ -11579,7 +11591,7 @@
         <x:v>timeline</x:v>
       </x:c>
       <x:c r="C14" s="18" t="str">
-        <x:v>Finished_Cosmo</x:v>
+        <x:v>Finished_Cosmopolitan</x:v>
       </x:c>
       <x:c r="D14" s="18" t="str">
         <x:v>완성 연출 — 앵커 4종만 유지(절차적 합성 방침, 30종 전부 제작 안 함)</x:v>
@@ -11609,7 +11621,7 @@
         <x:v>timeline</x:v>
       </x:c>
       <x:c r="C15" s="18" t="str">
-        <x:v>Finished_DryMarthini</x:v>
+        <x:v>Finished_DryMartini</x:v>
       </x:c>
       <x:c r="D15" s="18" t="str">
         <x:v>\E</x:v>
@@ -11639,7 +11651,7 @@
         <x:v>timeline</x:v>
       </x:c>
       <x:c r="C16" s="18" t="str">
-        <x:v>Finished_Ginfizz</x:v>
+        <x:v>Finished_GinFizz</x:v>
       </x:c>
       <x:c r="D16" s="18" t="str">
         <x:v>\E</x:v>
@@ -11669,7 +11681,7 @@
         <x:v>timeline</x:v>
       </x:c>
       <x:c r="C17" s="18" t="str">
-        <x:v>Finished_kalua</x:v>
+        <x:v>Finished_KahluaMilk</x:v>
       </x:c>
       <x:c r="D17" s="18" t="str">
         <x:v>\E</x:v>
@@ -11729,7 +11741,7 @@
         <x:v>timeline</x:v>
       </x:c>
       <x:c r="C19" s="18" t="str">
-        <x:v>Serve_Dry</x:v>
+        <x:v>Serve_DryMartini</x:v>
       </x:c>
       <x:c r="D19" s="18" t="str">
         <x:v>\E</x:v>
@@ -11759,7 +11771,7 @@
         <x:v>timeline</x:v>
       </x:c>
       <x:c r="C20" s="18" t="str">
-        <x:v>Serve_Ginfizz</x:v>
+        <x:v>Serve_GinFizz</x:v>
       </x:c>
       <x:c r="D20" s="18" t="str">
         <x:v>\E</x:v>
@@ -11789,7 +11801,7 @@
         <x:v>timeline</x:v>
       </x:c>
       <x:c r="C21" s="18" t="str">
-        <x:v>Serve_kalua</x:v>
+        <x:v>Serve_KahluaMilk</x:v>
       </x:c>
       <x:c r="D21" s="18" t="str">
         <x:v>\E</x:v>
@@ -12036,7 +12048,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb196b9d94b4e444a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0dabc09ed498403a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -12860,7 +12872,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd13a6a5183ba460e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R920a8d1541d54a44"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -13547,7 +13559,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb2a6dfb1dfb84720"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1d24fa9bf47448ba"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -13848,7 +13860,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R681897db35fe4e6e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R668a9dc1b06942bc"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -14098,7 +14110,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R938574ae64254666"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Raff6751f765640ac"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -14918,7 +14930,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R84f3671b153141c8"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb67baaf3167447c4"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -15729,7 +15741,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8cd1198dd1974bdf"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R182103cc158549be"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -16422,7 +16434,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5fdac43480a544f7"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfe2c1583eb754ed2"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -19119,6 +19131,37 @@
         <x:v>scenes_format_06</x:v>
       </x:c>
     </x:row>
+    <x:row r="70" ht="30" customHeight="1">
+      <x:c r="A70" s="30" t="str">
+        <x:v>tl_samho_arrive</x:v>
+      </x:c>
+      <x:c r="B70" s="30"/>
+      <x:c r="C70" s="30"/>
+      <x:c r="D70" s="30"/>
+      <x:c r="E70" s="30"/>
+      <x:c r="F70" s="30"/>
+      <x:c r="G70" s="30"/>
+      <x:c r="H70" s="30"/>
+      <x:c r="I70" s="30"/>
+      <x:c r="J70" s="31" t="str">
+        <x:v>script/street</x:v>
+      </x:c>
+      <x:c r="K70" s="31" t="str">
+        <x:v>scene_tl_samho_arrive</x:v>
+      </x:c>
+      <x:c r="L70" s="31" t="str">
+        <x:v>script_street</x:v>
+      </x:c>
+      <x:c r="M70" s="31" t="str">
+        <x:v>scenes</x:v>
+      </x:c>
+      <x:c r="N70" s="31" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="O70" s="31" t="str">
+        <x:v>scenes_format_06</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="K6:K69">
     <x:cfRule type="duplicateValues" dxfId="2" priority="1"/>
@@ -19140,7 +19183,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R151599bbacd04f90"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd988736d5e174fe7"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -52045,6 +52088,144 @@
         <x:v>steps_format_25</x:v>
       </x:c>
     </x:row>
+    <x:row r="671" ht="30" customHeight="1">
+      <x:c r="A671" s="31" t="str">
+        <x:v>tl_samho_arrive</x:v>
+      </x:c>
+      <x:c r="B671" s="30" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C671" s="30" t="str">
+        <x:v>say</x:v>
+      </x:c>
+      <x:c r="D671" s="30" t="str">
+        <x:v>samho</x:v>
+      </x:c>
+      <x:c r="E671" s="30"/>
+      <x:c r="F671" s="30" t="str">
+        <x:v>잠깐....!!!!!</x:v>
+      </x:c>
+      <x:c r="G671" s="30"/>
+      <x:c r="H671" s="30" t="str">
+        <x:v>dlg_tl_samho_arrive_001</x:v>
+      </x:c>
+      <x:c r="I671" s="30"/>
+      <x:c r="J671" s="30"/>
+      <x:c r="K671" s="30" t="str">
+        <x:v>auto</x:v>
+      </x:c>
+      <x:c r="L671" s="30"/>
+      <x:c r="M671" s="31" t="str">
+        <x:v>script/street</x:v>
+      </x:c>
+      <x:c r="N671" s="31" t="str">
+        <x:v>dlg_tl_samho_arrive_001</x:v>
+      </x:c>
+      <x:c r="O671" s="31" t="str">
+        <x:v>scene_tl_samho_arrive</x:v>
+      </x:c>
+      <x:c r="P671" s="31" t="str">
+        <x:v>steps</x:v>
+      </x:c>
+      <x:c r="Q671" s="31" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R671" s="31" t="str">
+        <x:v>steps_format_17</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="672" ht="30" customHeight="1">
+      <x:c r="A672" s="31" t="str">
+        <x:v>tl_samho_arrive</x:v>
+      </x:c>
+      <x:c r="B672" s="30" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C672" s="30" t="str">
+        <x:v>say</x:v>
+      </x:c>
+      <x:c r="D672" s="30" t="str">
+        <x:v>samho</x:v>
+      </x:c>
+      <x:c r="E672" s="30"/>
+      <x:c r="F672" s="30" t="str">
+        <x:v>...후....후 같이 올라가...</x:v>
+      </x:c>
+      <x:c r="G672" s="30"/>
+      <x:c r="H672" s="30" t="str">
+        <x:v>dlg_tl_samho_arrive_002</x:v>
+      </x:c>
+      <x:c r="I672" s="30"/>
+      <x:c r="J672" s="30"/>
+      <x:c r="K672" s="30" t="str">
+        <x:v>auto</x:v>
+      </x:c>
+      <x:c r="L672" s="30"/>
+      <x:c r="M672" s="31" t="str">
+        <x:v>script/street</x:v>
+      </x:c>
+      <x:c r="N672" s="31" t="str">
+        <x:v>dlg_tl_samho_arrive_002</x:v>
+      </x:c>
+      <x:c r="O672" s="31" t="str">
+        <x:v>scene_tl_samho_arrive</x:v>
+      </x:c>
+      <x:c r="P672" s="31" t="str">
+        <x:v>steps</x:v>
+      </x:c>
+      <x:c r="Q672" s="31" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="R672" s="31" t="str">
+        <x:v>steps_format_17</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="673" ht="30" customHeight="1">
+      <x:c r="A673" s="31" t="str">
+        <x:v>tl_samho_arrive</x:v>
+      </x:c>
+      <x:c r="B673" s="30" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C673" s="30" t="str">
+        <x:v>say</x:v>
+      </x:c>
+      <x:c r="D673" s="30" t="str">
+        <x:v>luna</x:v>
+      </x:c>
+      <x:c r="E673" s="30"/>
+      <x:c r="F673" s="30" t="str">
+        <x:v>..?</x:v>
+      </x:c>
+      <x:c r="G673" s="30"/>
+      <x:c r="H673" s="30" t="str">
+        <x:v>dlg_tl_samho_arrive_003</x:v>
+      </x:c>
+      <x:c r="I673" s="30"/>
+      <x:c r="J673" s="30"/>
+      <x:c r="K673" s="30" t="str">
+        <x:v>auto</x:v>
+      </x:c>
+      <x:c r="L673" s="30"/>
+      <x:c r="M673" s="31" t="str">
+        <x:v>script/street</x:v>
+      </x:c>
+      <x:c r="N673" s="31" t="str">
+        <x:v>dlg_tl_samho_arrive_003</x:v>
+      </x:c>
+      <x:c r="O673" s="31" t="str">
+        <x:v>scene_tl_samho_arrive</x:v>
+      </x:c>
+      <x:c r="P673" s="31" t="str">
+        <x:v>steps</x:v>
+      </x:c>
+      <x:c r="Q673" s="31" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="R673" s="31" t="str">
+        <x:v>steps_format_17</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="N6:N670">
     <x:cfRule type="duplicateValues" dxfId="3" priority="1"/>
@@ -52063,7 +52244,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R069d6d474c0d4813"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R40b0bb661d544c3f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -52501,7 +52682,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8340aa3e466c4c35"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R82f4a73ada2f4a12"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -54105,7 +54286,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfc4ec12ab30a4f14"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra02ca87e003c47d9"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -54456,7 +54637,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R756d1c06ab16481a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra466fe41b5524b7b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -55853,7 +56034,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbda31cae6f1b451d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R89858e28d452468f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/HumanBartender/outputs/20260915-content-editing/HumanBartender_C_Content.xlsx
+++ b/HumanBartender/outputs/20260915-content-editing/HumanBartender_C_Content.xlsx
@@ -2,29 +2,29 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Index" sheetId="1" r:id="R2d02c8778e6b4d1c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SourceInventory" sheetId="2" r:id="R7aa197b8152147e4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ScriptFiles" sheetId="3" r:id="Ra4682b50a0b148c0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Scenes" sheetId="4" r:id="R86a2495b5a41422f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Steps" sheetId="5" r:id="R6022f6b24f5e4ef2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BarChoiceGroups" sheetId="6" r:id="R1920eaad35524d88"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BarChoices" sheetId="7" r:id="R656a2cf803f74efc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="StreetChoices" sheetId="8" r:id="Rd82cd9cc601e4174"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="InteractPoints" sheetId="9" r:id="Re8fdda4fc0514f91"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DialogueFlows" sheetId="10" r:id="R29cb44e427904dfd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Characters" sheetId="11" r:id="R48e631238b324110"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CharacterExpressions" sheetId="12" r:id="R943c677b14c84b24"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AnimationCharacters" sheetId="13" r:id="R48f93660e3db4103"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Expressions" sheetId="14" r:id="Re1eaabcc6e6c4bb7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ExpressionParts" sheetId="15" r:id="R06920f67e4bb404b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cutscenes" sheetId="16" r:id="Re8b0ff7fc3b64038"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FieldAnimations" sheetId="17" r:id="R944e47d58339483a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Spots" sheetId="18" r:id="R410166b6498343f6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TextTags" sheetId="19" r:id="Rb96d81c27cdf4519"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dossier" sheetId="20" r:id="R501a4e8af1854446"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FieldGuide" sheetId="21" r:id="R5b2189c535054d4f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="StepTypes" sheetId="22" r:id="R4d006ba1a29d42a4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ReadMe" sheetId="23" r:id="Rb497c00603fd47e2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Index" sheetId="1" r:id="Rdc5e3a8be2c2475d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SourceInventory" sheetId="2" r:id="R73c30908358f4c5e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ScriptFiles" sheetId="3" r:id="Rc4faa946f5c749e2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Scenes" sheetId="4" r:id="Rdd7c3a323eea4896"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Steps" sheetId="5" r:id="Rfc3218ec8c944423"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BarChoiceGroups" sheetId="6" r:id="Reeff7e6e2b0a4dc8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BarChoices" sheetId="7" r:id="Re6fbe283bc544918"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="StreetChoices" sheetId="8" r:id="Ra3c8ec51d925408f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="InteractPoints" sheetId="9" r:id="R2bfb32ab19a24bee"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DialogueFlows" sheetId="10" r:id="R97866d7226604ce5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Characters" sheetId="11" r:id="R9900772f4f9c4f69"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CharacterExpressions" sheetId="12" r:id="R0bd74a300a264f6b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AnimationCharacters" sheetId="13" r:id="R2d6e5788c9a14da9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Expressions" sheetId="14" r:id="R0f579be09aeb41c1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ExpressionParts" sheetId="15" r:id="R9882d745086543f6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cutscenes" sheetId="16" r:id="Ra525a9ab88ba4022"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FieldAnimations" sheetId="17" r:id="R1d84114c60e84a66"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Spots" sheetId="18" r:id="R7243652980774eb6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TextTags" sheetId="19" r:id="Rf9050e33696d4347"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dossier" sheetId="20" r:id="R45d2bab495e54c9f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FieldGuide" sheetId="21" r:id="R3c91e66b829b443b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="StepTypes" sheetId="22" r:id="R3a35629a8f73453e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ReadMe" sheetId="23" r:id="Rc80721bb77a24699"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -2198,7 +2198,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Red768813958a413b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd3e96fc9821d4880"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3273,7 +3273,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1e2d547b947043ed"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2beed760bd1a4622"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4310,7 +4310,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1ffe5a94c5214dbf"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R570d94cb0dbb46fe"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5180,7 +5180,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R59065372d4ce4194"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R14cf1519dc25410f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8110,7 +8110,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R76d0653bc8c84fbd"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfceeb65a9bfa42ce"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11238,7 +11238,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re262c3f04fa843d5"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R06040c38e2764edb"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -12048,7 +12048,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0dabc09ed498403a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra87bea74719046e5"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -12872,7 +12872,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R920a8d1541d54a44"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9c7e5506cc784c0e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -13559,7 +13559,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1d24fa9bf47448ba"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb96d80dfc4894e4e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -13860,7 +13860,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R668a9dc1b06942bc"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra5ebe4dcff2b4687"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -14110,7 +14110,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Raff6751f765640ac"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf454f6a4759d4a36"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -14930,7 +14930,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb67baaf3167447c4"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R58572677d5f34b66"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -15741,7 +15741,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R182103cc158549be"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3b01ba1aa6a54855"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -16434,7 +16434,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfe2c1583eb754ed2"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7814a34f97164a8f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -19183,7 +19183,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd988736d5e174fe7"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R03896c3977e64845"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -19513,7 +19513,7 @@
         <x:v>default</x:v>
       </x:c>
       <x:c r="F9" s="18" t="str">
-        <x:v>방금 내가 무슨 말을 했는지 듣긴 한 거야?</x:v>
+        <x:v>방금 내가 무슨 말을 했는지 &lt;fx=reproach&gt;듣긴 한 거야?&lt;/fx&gt;</x:v>
       </x:c>
       <x:c r="G9" s="18" t="str">
         <x:v>Did you hear a word of what I just said?</x:v>
@@ -19965,7 +19965,7 @@
         <x:v>fail</x:v>
       </x:c>
       <x:c r="F18" s="18" t="str">
-        <x:v>또 딴생각하지.</x:v>
+        <x:v>&lt;fx=mutter&gt;또&lt;/fx&gt; &lt;fx=burst&gt;딴생각하지.&lt;/fx&gt;</x:v>
       </x:c>
       <x:c r="G18" s="18" t="str">
         <x:v>You're drifting off again.</x:v>
@@ -22179,7 +22179,7 @@
         <x:v>success</x:v>
       </x:c>
       <x:c r="F62" s="18" t="str">
-        <x:v>…생각보다 재능이 있군.</x:v>
+        <x:v>…생각보다 &lt;fx=admire&gt;재능이 있군&lt;/fx&gt;.</x:v>
       </x:c>
       <x:c r="G62" s="18" t="str">
         <x:v>...More talent than I expected.</x:v>
@@ -22493,7 +22493,7 @@
         <x:v>default</x:v>
       </x:c>
       <x:c r="F68" s="18" t="str">
-        <x:v>괜찮군.</x:v>
+        <x:v>&lt;fx=approve&gt;괜찮군&lt;/fx&gt;.</x:v>
       </x:c>
       <x:c r="G68" s="18" t="str">
         <x:v>Not bad.</x:v>
@@ -22755,7 +22755,7 @@
         <x:v>fail</x:v>
       </x:c>
       <x:c r="F73" s="18" t="str">
-        <x:v>아직 손님에게 내놓기엔 완성도가 부족한데.</x:v>
+        <x:v>아직 손님에게 내놓기엔 완성도가 &lt;fx=disappoint&gt;부족한데&lt;/fx&gt;.</x:v>
       </x:c>
       <x:c r="G73" s="18" t="str">
         <x:v>This isn't ready to serve to a customer yet.</x:v>
@@ -22860,7 +22860,7 @@
       </x:c>
       <x:c r="F75" s="18" t="str">
         <x:v>이런 식이면 곤란한데, 루나.
-제대로 만들어.</x:v>
+&lt;fx=command&gt;제대로 만들어.&lt;/fx&gt;</x:v>
       </x:c>
       <x:c r="G75" s="18" t="str">
         <x:v>This won't do, Luna.
@@ -23669,7 +23669,7 @@
         <x:v>default</x:v>
       </x:c>
       <x:c r="F91" s="18" t="str">
-        <x:v>좋아. 처음에는 그렇게 시작하는 거지.</x:v>
+        <x:v>&lt;fx=encourage&gt;좋아.&lt;/fx&gt; 처음에는 그렇게 시작하는 거지.</x:v>
       </x:c>
       <x:c r="G91" s="18" t="str">
         <x:v>Good. That's how everyone starts.</x:v>
@@ -24125,10 +24125,10 @@
         <x:v>default</x:v>
       </x:c>
       <x:c r="F100" s="18" t="str">
-        <x:v>오늘은 이걸로 끝이니까 먼저 집으로 가.</x:v>
+        <x:v>진토닉은 이 정도면 됐어. 잠깐 숨 좀 돌려.</x:v>
       </x:c>
       <x:c r="G100" s="18" t="str">
-        <x:v>That's it for today. Head home ahead of me.</x:v>
+        <x:v>That covers the Gin and Tonic. Take a breather.</x:v>
       </x:c>
       <x:c r="H100" s="18" t="str">
         <x:v>dlg_d1_tutorial_wrap_020</x:v>
@@ -24175,10 +24175,10 @@
         <x:v>default</x:v>
       </x:c>
       <x:c r="F101" s="18" t="str">
-        <x:v>보스는 같이 안 가는 겁니까?</x:v>
+        <x:v>보스는 아직 남으시는 겁니까?</x:v>
       </x:c>
       <x:c r="G101" s="18" t="str">
-        <x:v>You're not coming, Boss?</x:v>
+        <x:v>Are you staying a little longer, Boss?</x:v>
       </x:c>
       <x:c r="H101" s="18" t="str">
         <x:v>dlg_d1_tutorial_wrap_021</x:v>
@@ -24225,10 +24225,10 @@
         <x:v>default</x:v>
       </x:c>
       <x:c r="F102" s="18" t="str">
-        <x:v>그래. 원래 오늘은 쉬는 날이지만 거절할 수 없는 &lt;world&gt;손님&lt;/world&gt;이 있어서 같이 못 가.</x:v>
+        <x:v>그래. 오늘은 쉬는 날이지만 거절할 수 없는 &lt;world&gt;손님&lt;/world&gt;이 한 명 오기로 했어.</x:v>
       </x:c>
       <x:c r="G102" s="18" t="str">
-        <x:v>No. Today was supposed to be my day off, but there's a &lt;world&gt;guest&lt;/world&gt; I can't turn away.</x:v>
+        <x:v>Yes. Today's my day off, but there's a &lt;world&gt;guest&lt;/world&gt; I can't turn away.</x:v>
       </x:c>
       <x:c r="H102" s="18" t="str">
         <x:v>dlg_d1_tutorial_wrap_022</x:v>
@@ -24275,10 +24275,10 @@
         <x:v>default</x:v>
       </x:c>
       <x:c r="F103" s="18" t="str">
-        <x:v>물론 앞으로도 교대 근무로 할 거라 출퇴근을 같이 하진 못할 거다.</x:v>
+        <x:v>앞으로는 교대 근무로 할 거니까 손님 응대는 차차 익혀.</x:v>
       </x:c>
       <x:c r="G103" s="18" t="str">
-        <x:v>We'll be working in shifts from here on anyway, so don't expect us to commute together.</x:v>
+        <x:v>We'll work in shifts from now on. You'll get used to serving customers.</x:v>
       </x:c>
       <x:c r="H103" s="18" t="str">
         <x:v>dlg_d1_tutorial_wrap_023</x:v>
@@ -24375,10 +24375,10 @@
         <x:v>default</x:v>
       </x:c>
       <x:c r="F105" s="18" t="str">
-        <x:v>밖에서 처음 보는 사람이랑 말하거나 딴 길로 새지 말고 바로 집으로 가.</x:v>
+        <x:v>곧 올 거야. 아까 배운 대로 차분히 해.</x:v>
       </x:c>
       <x:c r="G105" s="18" t="str">
-        <x:v>Don't talk to strangers out there, and don't wander — go straight home.</x:v>
+        <x:v>He'll be here soon. Stay calm and use what you just learned.</x:v>
       </x:c>
       <x:c r="H105" s="18" t="str">
         <x:v>dlg_d1_tutorial_wrap_025</x:v>
@@ -52244,7 +52244,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R40b0bb661d544c3f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R241b307e9c1747c5"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -52682,7 +52682,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R82f4a73ada2f4a12"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5babcb5a5bff46c0"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -54286,7 +54286,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra02ca87e003c47d9"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8899bf88cd4440db"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -54637,7 +54637,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra466fe41b5524b7b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R93118a37bf10482a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -56034,7 +56034,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R89858e28d452468f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb12baf135d234bb1"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/HumanBartender/outputs/20260915-content-editing/HumanBartender_C_Content.xlsx
+++ b/HumanBartender/outputs/20260915-content-editing/HumanBartender_C_Content.xlsx
@@ -2,29 +2,29 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Index" sheetId="1" r:id="Rdc5e3a8be2c2475d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SourceInventory" sheetId="2" r:id="R73c30908358f4c5e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ScriptFiles" sheetId="3" r:id="Rc4faa946f5c749e2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Scenes" sheetId="4" r:id="Rdd7c3a323eea4896"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Steps" sheetId="5" r:id="Rfc3218ec8c944423"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BarChoiceGroups" sheetId="6" r:id="Reeff7e6e2b0a4dc8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BarChoices" sheetId="7" r:id="Re6fbe283bc544918"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="StreetChoices" sheetId="8" r:id="Ra3c8ec51d925408f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="InteractPoints" sheetId="9" r:id="R2bfb32ab19a24bee"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DialogueFlows" sheetId="10" r:id="R97866d7226604ce5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Characters" sheetId="11" r:id="R9900772f4f9c4f69"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CharacterExpressions" sheetId="12" r:id="R0bd74a300a264f6b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AnimationCharacters" sheetId="13" r:id="R2d6e5788c9a14da9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Expressions" sheetId="14" r:id="R0f579be09aeb41c1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ExpressionParts" sheetId="15" r:id="R9882d745086543f6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cutscenes" sheetId="16" r:id="Ra525a9ab88ba4022"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FieldAnimations" sheetId="17" r:id="R1d84114c60e84a66"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Spots" sheetId="18" r:id="R7243652980774eb6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TextTags" sheetId="19" r:id="Rf9050e33696d4347"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dossier" sheetId="20" r:id="R45d2bab495e54c9f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FieldGuide" sheetId="21" r:id="R3c91e66b829b443b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="StepTypes" sheetId="22" r:id="R3a35629a8f73453e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ReadMe" sheetId="23" r:id="Rc80721bb77a24699"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Index" sheetId="1" r:id="R82ada2fca7e248db"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SourceInventory" sheetId="2" r:id="R38a95a67921247aa"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ScriptFiles" sheetId="3" r:id="R0df5d044beb44ee7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Scenes" sheetId="4" r:id="R4af82bb27ded4222"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Steps" sheetId="5" r:id="R61910bfafc564ab4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BarChoiceGroups" sheetId="6" r:id="R19a3d76eb2244e19"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BarChoices" sheetId="7" r:id="Raae0d768151b4a1e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="StreetChoices" sheetId="8" r:id="R107517e340ee40ef"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="InteractPoints" sheetId="9" r:id="R2d120e0cfe7c4776"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DialogueFlows" sheetId="10" r:id="R7d7c38e70927469e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Characters" sheetId="11" r:id="R8ba8b37887ec4fc1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CharacterExpressions" sheetId="12" r:id="R710581e67d2c4773"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AnimationCharacters" sheetId="13" r:id="R665b0ac479db441b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Expressions" sheetId="14" r:id="Rf5576f728413413b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ExpressionParts" sheetId="15" r:id="Rcd41bc67d46c41fe"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cutscenes" sheetId="16" r:id="R28aea2bad0ce459e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FieldAnimations" sheetId="17" r:id="R1e58148c3b314a56"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Spots" sheetId="18" r:id="R4a3290d997ea44ed"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TextTags" sheetId="19" r:id="R0b27115ef7284664"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dossier" sheetId="20" r:id="Ra4fc9811386d4fe5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FieldGuide" sheetId="21" r:id="R7b2c8e210f524ee3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="StepTypes" sheetId="22" r:id="Rad0d5dab1d0c4c6e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ReadMe" sheetId="23" r:id="Rcfbc39d900924175"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -2198,7 +2198,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd3e96fc9821d4880"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R64d153f418ed4ec6"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3273,7 +3273,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2beed760bd1a4622"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4ac7dcafa439471b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4310,7 +4310,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R570d94cb0dbb46fe"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd8e150f407ad429c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5180,7 +5180,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R14cf1519dc25410f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc786823c6fa2461e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8110,7 +8110,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfceeb65a9bfa42ce"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R613251d962704c01"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11238,7 +11238,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R06040c38e2764edb"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1f909d5d74c94a29"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -12048,7 +12048,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra87bea74719046e5"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R056a9d6c0fbb455c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -12872,7 +12872,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9c7e5506cc784c0e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R245d4dfb4cfe4937"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -13559,7 +13559,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb96d80dfc4894e4e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rca43548949624665"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -13860,7 +13860,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra5ebe4dcff2b4687"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R53c31333cebc4bd2"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -14110,7 +14110,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf454f6a4759d4a36"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc16bb92fa4564f69"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -14930,7 +14930,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R58572677d5f34b66"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2acb788299a04fae"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -15741,7 +15741,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3b01ba1aa6a54855"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4f44e50694b846c6"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -16434,7 +16434,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7814a34f97164a8f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R990552552b854c86"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -19183,7 +19183,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R03896c3977e64845"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3581c745304345ea"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -19663,7 +19663,7 @@
         <x:v>default</x:v>
       </x:c>
       <x:c r="F12" s="18" t="str">
-        <x:v>집중해. 이제 와서 관두지도 못한다고.</x:v>
+        <x:v>&lt;shake amp=0.5 hz=16&gt;집중해.&lt;/shake&gt; 이제 와서 관두지도 못한다고.</x:v>
       </x:c>
       <x:c r="G12" s="18" t="str">
         <x:v>Focus. It's too late to quit now.</x:v>
@@ -19863,7 +19863,7 @@
         <x:v>default</x:v>
       </x:c>
       <x:c r="F16" s="18" t="str">
-        <x:v>&lt;order&gt;진토닉&lt;/order&gt; 하나만 만들 수 있게 되면 더는 확인하지 않을 거야.
+        <x:v>&lt;order&gt;진토닉&lt;/order&gt; &lt;pop peak=1.11 duration=0.12&gt;하나만&lt;/pop&gt; 만들 수 있게 되면 더는 확인하지 않을 거야.
 금방 하는 거니까 지루해도 참아.</x:v>
       </x:c>
       <x:c r="G16" s="18" t="str">
@@ -19915,7 +19915,7 @@
         <x:v>default</x:v>
       </x:c>
       <x:c r="F17" s="18" t="str">
-        <x:v>(진과 탄산수를 섞는 게 그렇게 어려운 일일까.)</x:v>
+        <x:v>(진과 탄산수를 섞는 게 &lt;wave amp=0.45 hz=1.4 phase=0.55&gt;그렇게 어려운 일일까&lt;/wave&gt;.)</x:v>
       </x:c>
       <x:c r="G17" s="18" t="str">
         <x:v>(Can mixing gin and carbonated water really be that difficult?)</x:v>
@@ -20423,7 +20423,7 @@
         <x:v>default</x:v>
       </x:c>
       <x:c r="F27" s="18" t="str">
-        <x:v>이유가 있습니까?</x:v>
+        <x:v>&lt;wave amp=0.45 hz=1.4 phase=0.6&gt;이유가 있습니까?&lt;/wave&gt;</x:v>
       </x:c>
       <x:c r="G27" s="18" t="str">
         <x:v>Is there a reason?</x:v>
@@ -20473,7 +20473,7 @@
         <x:v>default</x:v>
       </x:c>
       <x:c r="F28" s="18" t="str">
-        <x:v>“진토닉 하나도 제대로 만들지 못한다면,
+        <x:v>“&lt;pop peak=1.11 duration=0.12&gt;진토닉 하나도 제대로 만들지 못한다면&lt;/pop&gt;,
 다른 칵테일을 배울 필요도 없다.” 이게 전에 있던 마스터가 남긴 방침이야.</x:v>
       </x:c>
       <x:c r="G28" s="18" t="str">
@@ -20827,7 +20827,7 @@
         <x:v>default</x:v>
       </x:c>
       <x:c r="F35" s="18" t="str">
-        <x:v>생각보다 유용한 칩이었네요.</x:v>
+        <x:v>&lt;wave amp=0.45 hz=1.4 phase=0.6&gt;생각보다 유용한 칩&lt;/wave&gt;이었네요.</x:v>
       </x:c>
       <x:c r="G35" s="18" t="str">
         <x:v>The chip is more useful than I expected.</x:v>
@@ -20877,7 +20877,7 @@
         <x:v>default</x:v>
       </x:c>
       <x:c r="F36" s="18" t="str">
-        <x:v>그거 만들겠다고 전 마스터가 고생 좀 했지.</x:v>
+        <x:v>그거 만들겠다고 전 마스터가 &lt;slow&gt;고생 좀 했지&lt;/slow&gt;.</x:v>
       </x:c>
       <x:c r="G36" s="18" t="str">
         <x:v>The old master went through hell building that thing.</x:v>
@@ -21081,7 +21081,7 @@
         <x:v>default</x:v>
       </x:c>
       <x:c r="F40" s="18" t="str">
-        <x:v>기억은 하는군. 각 방법이 뭐가 다른지에 대한 설명도 필요하나?</x:v>
+        <x:v>&lt;pop peak=1.11 duration=0.12&gt;기억은 하는군.&lt;/pop&gt; 각 방법이 뭐가 다른지에 대한 설명도 필요하나?</x:v>
       </x:c>
       <x:c r="G40" s="18" t="str">
         <x:v>So you do remember. Need me to explain how they differ?</x:v>
@@ -21437,7 +21437,7 @@
         <x:v>default</x:v>
       </x:c>
       <x:c r="F47" s="18" t="str">
-        <x:v>평범한 사람이라면 전부 기억하기 힘들 것 같습니다.</x:v>
+        <x:v>평범한 사람이라면 &lt;wave amp=0.45 hz=1.4 phase=0.6&gt;전부 기억하기 힘들 것 같습니다.&lt;/wave&gt;</x:v>
       </x:c>
       <x:c r="G47" s="18" t="str">
         <x:v>An ordinary person would struggle to remember all of this.</x:v>
@@ -21487,7 +21487,7 @@
         <x:v>default</x:v>
       </x:c>
       <x:c r="F48" s="18" t="str">
-        <x:v>그래. 그래도 넌 &lt;world&gt;평범한 사람&lt;/world&gt;이 아니잖아.</x:v>
+        <x:v>그래. 그래도 넌 &lt;pop peak=1.1 duration=0.14&gt;&lt;world&gt;평범한 사람&lt;/world&gt;&lt;/pop&gt;이 아니잖아.</x:v>
       </x:c>
       <x:c r="G48" s="18" t="str">
         <x:v>Right. But then, you're no &lt;world&gt;ordinary person&lt;/world&gt;.</x:v>
@@ -21537,7 +21537,7 @@
         <x:v>default</x:v>
       </x:c>
       <x:c r="F49" s="18" t="str">
-        <x:v>저는 평범하다고 생각합니다.</x:v>
+        <x:v>저는 &lt;pop peak=1.11 duration=0.12&gt;평범하다고&lt;/pop&gt; 생각합니다.</x:v>
       </x:c>
       <x:c r="G49" s="18" t="str">
         <x:v>I consider myself ordinary.</x:v>
@@ -22285,7 +22285,7 @@
         <x:v>default</x:v>
       </x:c>
       <x:c r="F64" s="18" t="str">
-        <x:v>그래. 기본적인 제조 수업은 끝이야.</x:v>
+        <x:v>그래. 기본적인 &lt;pop peak=1.14 duration=0.12&gt;제조 수업은 끝이야.&lt;/pop&gt;</x:v>
       </x:c>
       <x:c r="G64" s="18" t="str">
         <x:v>Yes. The basic mixing lessons are over.</x:v>
@@ -22599,7 +22599,7 @@
         <x:v>default</x:v>
       </x:c>
       <x:c r="F70" s="18" t="str">
-        <x:v>다행이네요.</x:v>
+        <x:v>&lt;wave amp=0.45 hz=1.4 phase=0.6&gt;다행이네요.&lt;/wave&gt;</x:v>
       </x:c>
       <x:c r="G70" s="18" t="str">
         <x:v>That's a relief.</x:v>
@@ -23213,7 +23213,7 @@
         <x:v>default</x:v>
       </x:c>
       <x:c r="F82" s="18" t="str">
-        <x:v>그러면 제 마음대로 만들어 주면 되는 건가요?</x:v>
+        <x:v>그러면 &lt;wave amp=0.45 hz=1.4 phase=0.6&gt;제 마음대로&lt;/wave&gt; 만들어 주면 되는 건가요?</x:v>
       </x:c>
       <x:c r="G82" s="18" t="str">
         <x:v>Then I may make whatever I like?</x:v>
@@ -23363,7 +23363,7 @@
         <x:v>default</x:v>
       </x:c>
       <x:c r="F85" s="18" t="str">
-        <x:v>애매한 주문이라도 최대한 &lt;world&gt;의도&lt;/world&gt;를 파악하려고 해 봐.
+        <x:v>애매한 주문이라도 최대한 &lt;pop peak=1.08 duration=0.12&gt;&lt;world&gt;의도&lt;/world&gt;&lt;/pop&gt;를 파악하려고 해 봐.
 눈앞에 있는 손님이 어떤 맛을 좋아할지도 생각해 보고.</x:v>
       </x:c>
       <x:c r="G85" s="18" t="str">
@@ -23465,7 +23465,7 @@
         <x:v>default</x:v>
       </x:c>
       <x:c r="F87" s="18" t="str">
-        <x:v>뭐든 해 보려는 마음가짐이 중요한 거지.</x:v>
+        <x:v>뭐든 해 보려는 &lt;pop peak=1.11 duration=0.12&gt;마음가짐&lt;/pop&gt;이 중요한 거지.</x:v>
       </x:c>
       <x:c r="G87" s="18" t="str">
         <x:v>What matters is the willingness to try.</x:v>
@@ -23719,7 +23719,7 @@
         <x:v>default</x:v>
       </x:c>
       <x:c r="F92" s="18" t="str">
-        <x:v>아직 배워야 될 게 또 남았나요?</x:v>
+        <x:v>아직 배워야 될 게 &lt;wave amp=0.45 hz=1.4 phase=0.6&gt;또 남았나요?&lt;/wave&gt;</x:v>
       </x:c>
       <x:c r="G92" s="18" t="str">
         <x:v>Is there more I need to learn?</x:v>
@@ -23923,7 +23923,7 @@
         <x:v>default</x:v>
       </x:c>
       <x:c r="F96" s="18" t="str">
-        <x:v>이제 가게에서는 크리스 말고 보스라고 불러.</x:v>
+        <x:v>이제 가게에서는 크리스 말고 &lt;pop peak=1.12 duration=0.14&gt;보스&lt;/pop&gt;라고 불러.</x:v>
       </x:c>
       <x:c r="G96" s="18" t="str">
         <x:v>From now on, in the bar, it's not 'Chris' — call me 'Boss.'</x:v>
@@ -24225,7 +24225,7 @@
         <x:v>default</x:v>
       </x:c>
       <x:c r="F102" s="18" t="str">
-        <x:v>그래. 오늘은 쉬는 날이지만 거절할 수 없는 &lt;world&gt;손님&lt;/world&gt;이 한 명 오기로 했어.</x:v>
+        <x:v>그래. 오늘은 쉬는 날이지만 &lt;slow&gt;거절할 수 없는&lt;/slow&gt; &lt;wave amp=0.45 hz=1.2&gt;&lt;world&gt;손님&lt;/world&gt;&lt;/wave&gt;이 한 명 오기로 했어.</x:v>
       </x:c>
       <x:c r="G102" s="18" t="str">
         <x:v>Yes. Today's my day off, but there's a &lt;world&gt;guest&lt;/world&gt; I can't turn away.</x:v>
@@ -24519,7 +24519,7 @@
         <x:v>default</x:v>
       </x:c>
       <x:c r="F108" s="18" t="str">
-        <x:v>…새 얼굴이군.</x:v>
+        <x:v>…&lt;slow&gt;새 얼굴이군.&lt;/slow&gt;</x:v>
       </x:c>
       <x:c r="G108" s="18" t="str">
         <x:v>...A new face.</x:v>
@@ -24769,7 +24769,7 @@
         <x:v>exact:gin_fizz</x:v>
       </x:c>
       <x:c r="F113" s="18" t="str">
-        <x:v>진피즈, 정석대로.</x:v>
+        <x:v>&lt;order&gt;진피즈&lt;/order&gt;, &lt;pop peak=1.1 duration=0.12&gt;정석대로&lt;/pop&gt;.</x:v>
       </x:c>
       <x:c r="G113" s="18" t="str">
         <x:v>Gin Fizz. By the book.</x:v>
@@ -24903,7 +24903,7 @@
         <x:v>default</x:v>
       </x:c>
       <x:c r="F116" s="18" t="str">
-        <x:v>…손끝이 좋군. 오늘이 처음이라고?</x:v>
+        <x:v>…&lt;wave amp=0.5 hz=1.5&gt;손끝이 좋군&lt;/wave&gt;. 오늘이 처음이라고?</x:v>
       </x:c>
       <x:c r="G116" s="18" t="str">
         <x:v>...Good hands. First day, you said?</x:v>
@@ -25003,7 +25003,7 @@
         <x:v>default</x:v>
       </x:c>
       <x:c r="F118" s="18" t="str">
-        <x:v>허. …이 가게, 오래 다녀야겠어.</x:v>
+        <x:v>허. …이 가게, &lt;wave amp=0.45 hz=1.4 phase=0.6&gt;오래 다녀야겠어.&lt;/wave&gt;</x:v>
       </x:c>
       <x:c r="G118" s="18" t="str">
         <x:v>Hah. ...I'll be coming here a long while yet.</x:v>
@@ -25525,7 +25525,7 @@
         <x:v>success</x:v>
       </x:c>
       <x:c r="F129" s="18" t="str">
-        <x:v>존나 맛있어.
+        <x:v>&lt;pop peak=1.14 duration=0.12&gt;존나 맛있어.&lt;/pop&gt;
 왜 맛있지?</x:v>
       </x:c>
       <x:c r="G129" s="18" t="str">
@@ -25897,7 +25897,7 @@
         <x:v>default</x:v>
       </x:c>
       <x:c r="F136" s="18" t="str">
-        <x:v>정성 들인 쓰레기. 형용할 수 없는 최악의 맛이지.</x:v>
+        <x:v>&lt;shake amp=0.5 hz=16&gt;정성 들인 쓰레기.&lt;/shake&gt; 형용할 수 없는 최악의 맛이지.</x:v>
       </x:c>
       <x:c r="G136" s="18" t="str">
         <x:v>Devoted garbage. The indescribable worst.</x:v>
@@ -26211,7 +26211,7 @@
         <x:v>default</x:v>
       </x:c>
       <x:c r="F142" s="18" t="str">
-        <x:v>크리스에 비하면 네가 만든 건 예술이지.
+        <x:v>크리스에 비하면 네가 만든 건 &lt;wave amp=0.55 hz=1.7 phase=0.6&gt;예술이지.&lt;/wave&gt;
 처음 봤을 때 어느 정도 예상하긴 했지만, 기대 이상이네. 이쁜이.
 앞으로 자주 와야겠는걸?</x:v>
       </x:c>
@@ -26635,7 +26635,7 @@
         <x:v>default</x:v>
       </x:c>
       <x:c r="F150" s="18" t="str">
-        <x:v>안 좋은 쪽으로는 전설이지.</x:v>
+        <x:v>안 좋은 쪽으로는 &lt;pop peak=1.11 duration=0.12&gt;전설이지.&lt;/pop&gt;</x:v>
       </x:c>
       <x:c r="G150" s="18" t="str">
         <x:v>It's legendary — in the worst way.</x:v>
@@ -26898,7 +26898,7 @@
       </x:c>
       <x:c r="F155" s="18" t="str">
         <x:v>그걸 너무 진지하게 분석하지 마.
-그냥 느낌으로 가는 거야, 느낌.</x:v>
+그냥 &lt;wave amp=0.55 hz=1.7 phase=0.6&gt;느낌으로 가는 거야, 느낌.&lt;/wave&gt;</x:v>
       </x:c>
       <x:c r="G155" s="18" t="str">
         <x:v>Don't analyze it so seriously.
@@ -27211,7 +27211,7 @@
         <x:v>fail</x:v>
       </x:c>
       <x:c r="F161" s="18" t="str">
-        <x:v>하지만 다음번에도 이렇게 만들어주면 나도 화낼 거라고.</x:v>
+        <x:v>하지만 다음번에도 이렇게 만들어주면 나도 &lt;shake amp=0.5 hz=16&gt;화낼 거라고.&lt;/shake&gt;</x:v>
       </x:c>
       <x:c r="G161" s="18" t="str">
         <x:v>But serve me this again next time, and I will get angry.</x:v>
@@ -27675,7 +27675,7 @@
         <x:v>default</x:v>
       </x:c>
       <x:c r="F170" s="18" t="str">
-        <x:v>(고양이가 좋아하는 칵테일… 그런 게 있는 건가?)</x:v>
+        <x:v>(고양이가 좋아하는 칵테일… &lt;wave amp=0.45 hz=1.4 phase=0.6&gt;그런 게 있는 건가?&lt;/wave&gt;)</x:v>
       </x:c>
       <x:c r="G170" s="18" t="str">
         <x:v>(A cocktail cats enjoy... does such a thing exist?)</x:v>
@@ -27859,7 +27859,7 @@
         <x:v>default</x:v>
       </x:c>
       <x:c r="F174" s="18" t="str">
-        <x:v>미야아옹.</x:v>
+        <x:v>&lt;wave amp=0.55 hz=1.7 phase=0.6&gt;미야아옹.&lt;/wave&gt;</x:v>
       </x:c>
       <x:c r="G174" s="18" t="str">
         <x:v>Meooow.</x:v>
@@ -28224,7 +28224,7 @@
       </x:c>
       <x:c r="F181" s="18" t="str">
         <x:v>실력이 꽤 괜찮나 보네.
-부비까지 만족시키다니.</x:v>
+&lt;pop peak=1.11 duration=0.12&gt;부비까지 만족시키다니.&lt;/pop&gt;</x:v>
       </x:c>
       <x:c r="G181" s="18" t="str">
         <x:v>Your skills must be decent.
@@ -29485,7 +29485,7 @@
         <x:v>default</x:v>
       </x:c>
       <x:c r="F206" s="18" t="str">
-        <x:v>손님 받아라!!!</x:v>
+        <x:v>&lt;fast&gt;&lt;shake amp=0.65 hz=18&gt;손님 받아라!!!&lt;/shake&gt;&lt;/fast&gt;</x:v>
       </x:c>
       <x:c r="G206" s="18" t="str">
         <x:v>Customer coming through!!!</x:v>
@@ -29585,7 +29585,7 @@
         <x:v>default</x:v>
       </x:c>
       <x:c r="F208" s="18" t="str">
-        <x:v>오랜만이야, 이쁜이. 진짜 여기서 일하고 있었구나.</x:v>
+        <x:v>&lt;wave amp=0.55 hz=1.7 phase=0.6&gt;오랜만이야, 이쁜이.&lt;/wave&gt; 진짜 여기서 일하고 있었구나.</x:v>
       </x:c>
       <x:c r="G208" s="18" t="str">
         <x:v>Long time no see, cutie. So you really are working here.</x:v>
@@ -30042,7 +30042,7 @@
       </x:c>
       <x:c r="F217" s="18" t="str">
         <x:v>나도 쫓겨났다니까?
-빌어먹을 영감탱이.</x:v>
+&lt;shake amp=0.65 hz=18&gt;빌어먹을 영감탱이.&lt;/shake&gt;</x:v>
       </x:c>
       <x:c r="G217" s="18" t="str">
         <x:v>He kicked me out too, you know?
@@ -30143,7 +30143,7 @@
         <x:v>default</x:v>
       </x:c>
       <x:c r="F219" s="18" t="str">
-        <x:v>걱정 마. 부비가 평범한 고양이는 아니거든.</x:v>
+        <x:v>걱정 마. 부비가 &lt;pop peak=1.11 duration=0.12&gt;평범한 고양이는 아니거든.&lt;/pop&gt;</x:v>
       </x:c>
       <x:c r="G219" s="18" t="str">
         <x:v>Don't worry. Bubi's no ordinary cat.</x:v>
@@ -30446,7 +30446,7 @@
       </x:c>
       <x:c r="F225" s="18" t="str">
         <x:v>난 날 내려다 보는 사람이 있으면 
-면상에 총알을 박아주고 싶은 병이있어.</x:v>
+&lt;shake amp=0.65 hz=18&gt;면상에 총알을 박아주고 싶은&lt;/shake&gt; 병이있어.</x:v>
       </x:c>
       <x:c r="G225" s="18" t="str">
         <x:v>I've got this condition — when someone looks down on me,
@@ -30698,7 +30698,7 @@
       </x:c>
       <x:c r="F230" s="18" t="str">
         <x:v>맞아 이 박스 덕분에 건방진 크리스가 아직 총에 맞지 않는거야.
-어떻게 보면 이 박스가 사람 하나 살려준 셈이지.</x:v>
+어떻게 보면 이 &lt;wave amp=0.55 hz=1.7 phase=0.6&gt;박스가 사람 하나 살려준 셈이지.&lt;/wave&gt;</x:v>
       </x:c>
       <x:c r="G230" s="18" t="str">
         <x:v>Exactly. Thanks to this box, that cocky Chris hasn't been shot yet.
@@ -30900,7 +30900,7 @@
       </x:c>
       <x:c r="F234" s="18" t="str">
         <x:v>음…
-나 같은 섹시한 레이디한테 어울리는 술로 부탁해.</x:v>
+나 같은 &lt;wave amp=0.55 hz=1.7 phase=0.6&gt;섹시한 레이디&lt;/wave&gt;한테 어울리는 술로 부탁해.</x:v>
       </x:c>
       <x:c r="G234" s="18" t="str">
         <x:v>Hmm...
@@ -31043,7 +31043,7 @@
         <x:v>default</x:v>
       </x:c>
       <x:c r="F237" s="18" t="str">
-        <x:v>남녀 불문하고 내 매력에 빠져 돈이나 임플란트까지 뜯어다 바치는
+        <x:v>남녀 불문하고 내 매력에 빠져 돈이나 &lt;pop peak=1.14 duration=0.12&gt;임플란트까지&lt;/pop&gt; 뜯어다 바치는
 매력을 가진 레이디라는 거지.</x:v>
       </x:c>
       <x:c r="G237" s="18" t="str">
@@ -31301,7 +31301,7 @@
         <x:v>default</x:v>
       </x:c>
       <x:c r="F242" s="18" t="str">
-        <x:v>그렇다면 섹시한 레이디란 건 많은 이들한테 쫓겨서 피곤한 사람이란 거네요.</x:v>
+        <x:v>그렇다면 섹시한 레이디란 건 많은 이들한테 &lt;wave amp=0.45 hz=1.4 phase=0.6&gt;쫓겨서 피곤한 사람&lt;/wave&gt;이란 거네요.</x:v>
       </x:c>
       <x:c r="G242" s="18" t="str">
         <x:v>So a 'sexy lady' is someone exhausted from being chased by many people.</x:v>
@@ -31351,7 +31351,7 @@
         <x:v>default</x:v>
       </x:c>
       <x:c r="F243" s="18" t="str">
-        <x:v>정확해. 내가 보기엔 루나 너도 재능이 충분히 있어 보여.
+        <x:v>&lt;pop peak=1.11 duration=0.12&gt;정확해.&lt;/pop&gt; 내가 보기엔 루나 너도 재능이 충분히 있어 보여.
 어때? 나한테 배워볼 생각은?</x:v>
       </x:c>
       <x:c r="G243" s="18" t="str">
@@ -31599,7 +31599,7 @@
         <x:v>default</x:v>
       </x:c>
       <x:c r="F248" s="18" t="str">
-        <x:v>오늘부터는 손님을 직접 받는다. 어제 배운 대로 할 수 있겠지?</x:v>
+        <x:v>오늘부터는 &lt;pop peak=1.14 duration=0.12&gt;손님을 직접 받는다.&lt;/pop&gt; 어제 배운 대로 할 수 있겠지?</x:v>
       </x:c>
       <x:c r="G248" s="18" t="str">
         <x:v>From tonight you take the guests yourself. You can do it the way I taught you, right?</x:v>
@@ -31799,7 +31799,7 @@
         <x:v>default</x:v>
       </x:c>
       <x:c r="F252" s="18" t="str">
-        <x:v>틀린 잔은 내가 물어준다. 두 번 틀리지만 마라.</x:v>
+        <x:v>틀린 잔은 내가 물어준다. &lt;shake amp=0.5 hz=16&gt;두 번 틀리지만 마라.&lt;/shake&gt;</x:v>
       </x:c>
       <x:c r="G252" s="18" t="str">
         <x:v>I'll cover the wrong ones. Just don't make the same mistake twice.</x:v>
@@ -31849,7 +31849,7 @@
         <x:v>default</x:v>
       </x:c>
       <x:c r="F253" s="18" t="str">
-        <x:v>좋아, 시작해보자. 간판 걸어라.</x:v>
+        <x:v>좋아, 시작해보자. &lt;pop peak=1.14 duration=0.12&gt;간판 걸어라.&lt;/pop&gt;</x:v>
       </x:c>
       <x:c r="G253" s="18" t="str">
         <x:v>All right. Let's open. Go flip the sign.</x:v>
@@ -32361,7 +32361,7 @@
         <x:v>default</x:v>
       </x:c>
       <x:c r="F263" s="18" t="str">
-        <x:v>그래도 첫날치고는 잘했나 보네.</x:v>
+        <x:v>그래도 &lt;pop peak=1.11 duration=0.12&gt;첫날치고는 잘했나 보네.&lt;/pop&gt;</x:v>
       </x:c>
       <x:c r="G263" s="18" t="str">
         <x:v>Seems you did well, for a first day.</x:v>
@@ -32462,7 +32462,7 @@
       </x:c>
       <x:c r="F265" s="18" t="str">
         <x:v>누가 소리 지르고 뭔갈 집어던지지는 않았잖아?
-그럼 잘한 거지.</x:v>
+&lt;wave amp=0.45 hz=1.4 phase=0.6&gt;그럼 잘한 거지.&lt;/wave&gt;</x:v>
       </x:c>
       <x:c r="G265" s="18" t="str">
         <x:v>Nobody screamed or threw anything, right?
@@ -32847,7 +32847,7 @@
         <x:v>default</x:v>
       </x:c>
       <x:c r="F273" s="18" t="str">
-        <x:v>보스.</x:v>
+        <x:v>&lt;pop peak=1.14 duration=0.12&gt;보스.&lt;/pop&gt;</x:v>
       </x:c>
       <x:c r="G273" s="18" t="str">
         <x:v>Boss.</x:v>
@@ -33049,7 +33049,7 @@
         <x:v>default</x:v>
       </x:c>
       <x:c r="F277" s="18" t="str">
-        <x:v>..너가?</x:v>
+        <x:v>..&lt;pop peak=1.11 duration=0.12&gt;너가?&lt;/pop&gt;</x:v>
       </x:c>
       <x:c r="G277" s="18" t="str">
         <x:v>..You?</x:v>
@@ -33454,7 +33454,7 @@
       </x:c>
       <x:c r="F285" s="18" t="str">
         <x:v>제가 생각하기엔 행복이란 건 
-일을 하지 않아도 되는 삶인 것 같습니다.</x:v>
+&lt;wave amp=0.45 hz=1.4 phase=0.6&gt;일을 하지 않아도 되는 삶&lt;/wave&gt;인 것 같습니다.</x:v>
       </x:c>
       <x:c r="G285" s="18" t="str">
         <x:v>In my analysis, happiness is
@@ -33505,7 +33505,7 @@
         <x:v>default</x:v>
       </x:c>
       <x:c r="F286" s="18" t="str">
-        <x:v>너 오늘 첫 출근이야. 앓는 소리는 짬 차면 해.</x:v>
+        <x:v>너 오늘 &lt;pop peak=1.11 duration=0.12&gt;첫 출근&lt;/pop&gt;이야. 앓는 소리는 짬 차면 해.</x:v>
       </x:c>
       <x:c r="G286" s="18" t="str">
         <x:v>It's your first shift. Earn some seniority before you start whining.</x:v>
@@ -33605,7 +33605,7 @@
         <x:v>default</x:v>
       </x:c>
       <x:c r="F288" s="18" t="str">
-        <x:v>또 몰래 재료 먹으면 안 돼.</x:v>
+        <x:v>또 &lt;shake amp=0.5 hz=16&gt;몰래 재료 먹으면 안 돼.&lt;/shake&gt;</x:v>
       </x:c>
       <x:c r="G288" s="18" t="str">
         <x:v>And no sneaking bites of the ingredients again.</x:v>
@@ -33847,7 +33847,7 @@
         <x:v>default</x:v>
       </x:c>
       <x:c r="F293" s="18" t="str">
-        <x:v>이번엔 올리브를 한 번……</x:v>
+        <x:v>이번엔 &lt;slow&gt;올리브를 한 번&lt;/slow&gt;……</x:v>
       </x:c>
       <x:c r="G293" s="18" t="str">
         <x:v>This time, maybe an olive......</x:v>
@@ -33947,7 +33947,7 @@
         <x:v>default</x:v>
       </x:c>
       <x:c r="F295" s="18" t="str">
-        <x:v>이게 라임이었나?</x:v>
+        <x:v>이게 &lt;wave amp=0.45 hz=1.4 phase=0.6&gt;라임이었나?&lt;/wave&gt;</x:v>
       </x:c>
       <x:c r="G295" s="18" t="str">
         <x:v>Was this a lime?</x:v>
@@ -34491,7 +34491,7 @@
         <x:v>event_surprise</x:v>
       </x:c>
       <x:c r="F306" s="18" t="str">
-        <x:v>ㅁ..뭐야! 니미랄!!!</x:v>
+        <x:v>ㅁ..&lt;fast&gt;&lt;shake amp=0.65 hz=18&gt;뭐야! 니미랄!!!&lt;/shake&gt;&lt;/fast&gt;</x:v>
       </x:c>
       <x:c r="G306" s="18" t="str">
         <x:v>Wh..what the! Son of a—!!!</x:v>
@@ -34791,7 +34791,7 @@
         <x:v>default</x:v>
       </x:c>
       <x:c r="F312" s="18" t="str">
-        <x:v>아쉽지만 '기다려 봐'라는 술은 없습니다.</x:v>
+        <x:v>아쉽지만 &lt;wave amp=0.55 hz=1.7 phase=0.6&gt;'기다려 봐'라는 술&lt;/wave&gt;은 없습니다.</x:v>
       </x:c>
       <x:c r="G312" s="18" t="str">
         <x:v>Unfortunately, we do not carry a drink called 'Hold On.'</x:v>
@@ -34992,7 +34992,7 @@
       </x:c>
       <x:c r="F316" s="18" t="str">
         <x:v>어쩐지 나보고 오늘 일찍 끝내고 오라더니…
-이 썩을 놈이 날 교육 자료로 써?</x:v>
+이 썩을 놈이 날 &lt;pop peak=1.11 duration=0.12&gt;교육 자료로 써?&lt;/pop&gt;</x:v>
       </x:c>
       <x:c r="G316" s="18" t="str">
         <x:v>No wonder he told me to close up early and come over...
@@ -35043,7 +35043,7 @@
         <x:v>default</x:v>
       </x:c>
       <x:c r="F317" s="18" t="str">
-        <x:v>교육 자료로 쓰기엔 많이 노후된 걸로 보입니다.</x:v>
+        <x:v>교육 자료로 쓰기엔 &lt;pop peak=1.11 duration=0.12&gt;많이 노후된&lt;/pop&gt; 걸로 보입니다.</x:v>
       </x:c>
       <x:c r="G317" s="18" t="str">
         <x:v>You appear too worn-out to serve as training material.</x:v>
@@ -35531,7 +35531,7 @@
         <x:v>default</x:v>
       </x:c>
       <x:c r="F327" s="18" t="str">
-        <x:v>이거 왜 맛있어?</x:v>
+        <x:v>이거 &lt;pop peak=1.14 duration=0.12&gt;왜 맛있어?&lt;/pop&gt;</x:v>
       </x:c>
       <x:c r="G327" s="18" t="str">
         <x:v>Why does this taste good?</x:v>
@@ -35635,7 +35635,7 @@
         <x:v>joy</x:v>
       </x:c>
       <x:c r="F329" s="18" t="str">
-        <x:v>아니. 그건 아니지만. 애송이가 만든 거라고 믿기지 않는군.</x:v>
+        <x:v>아니. 그건 아니지만. 애송이가 만든 거라고 &lt;wave amp=0.45 hz=1.4 phase=0.6&gt;믿기지 않는군.&lt;/wave&gt;</x:v>
       </x:c>
       <x:c r="G329" s="18" t="str">
         <x:v>No. It's not that. Just hard to believe a greenhorn made this.</x:v>
@@ -36157,7 +36157,7 @@
         <x:v>serious</x:v>
       </x:c>
       <x:c r="F339" s="18" t="str">
-        <x:v>진피즈긴 한데… 뭔가 어설퍼.</x:v>
+        <x:v>진피즈긴 한데… &lt;wave amp=0.45 hz=1.4 phase=0.6&gt;뭔가 어설퍼.&lt;/wave&gt;</x:v>
       </x:c>
       <x:c r="G339" s="18" t="str">
         <x:v>It's a Gin Fizz, sure... but something's clumsy about it.</x:v>
@@ -36417,7 +36417,7 @@
         <x:v>serious</x:v>
       </x:c>
       <x:c r="F344" s="18" t="str">
-        <x:v>얼마나 자신있으면 시키지도 않은 술을 주는 거지?</x:v>
+        <x:v>얼마나 자신있으면 &lt;pop peak=1.11 duration=0.12&gt;시키지도 않은 술&lt;/pop&gt;을 주는 거지?</x:v>
       </x:c>
       <x:c r="G344" s="18" t="str">
         <x:v>How confident do you have to be to serve a drink nobody ordered?</x:v>
@@ -36887,7 +36887,7 @@
         <x:v>anger</x:v>
       </x:c>
       <x:c r="F353" s="18" t="str">
-        <x:v>이게 술이냐?</x:v>
+        <x:v>&lt;shake amp=0.65 hz=18&gt;이게 술이냐?&lt;/shake&gt;</x:v>
       </x:c>
       <x:c r="G353" s="18" t="str">
         <x:v>You call this a drink?</x:v>
@@ -36991,7 +36991,7 @@
         <x:v>anger</x:v>
       </x:c>
       <x:c r="F355" s="18" t="str">
-        <x:v>아니, 나는 내 미각을 마비시키는 무언가를 쓰레기라 부르기로 했어.</x:v>
+        <x:v>아니, 나는 내 미각을 마비시키는 무언가를 &lt;shake amp=0.5 hz=16&gt;쓰레기&lt;/shake&gt;라 부르기로 했어.</x:v>
       </x:c>
       <x:c r="G355" s="18" t="str">
         <x:v>No. I've decided to call anything that paralyzes my taste buds garbage.</x:v>
@@ -37537,7 +37537,7 @@
         <x:v>serious</x:v>
       </x:c>
       <x:c r="F366" s="18" t="str">
-        <x:v>마시면 인생을 다시 생각하게 되는 맛이었지.</x:v>
+        <x:v>마시면 &lt;wave amp=0.45 hz=1.4 phase=0.6&gt;인생을 다시 생각하게 되는 맛&lt;/wave&gt;이었지.</x:v>
       </x:c>
       <x:c r="G366" s="18" t="str">
         <x:v>It was the kind of taste that makes you reconsider your whole life.</x:v>
@@ -37637,7 +37637,7 @@
         <x:v>serious</x:v>
       </x:c>
       <x:c r="F368" s="18" t="str">
-        <x:v>아니. 대체 어쩌다 내가 휘발유 맛이 나는 술을 마시고 있는
+        <x:v>아니. 대체 어쩌다 내가 &lt;pop peak=1.14 duration=0.12&gt;휘발유 맛&lt;/pop&gt;이 나는 술을 마시고 있는
 인생을 살게 되었는지 생각한 거야.</x:v>
       </x:c>
       <x:c r="G368" s="18" t="str">
@@ -37841,7 +37841,7 @@
         <x:v>anger</x:v>
       </x:c>
       <x:c r="F372" s="18" t="str">
-        <x:v>뭐? 이 썩을 놈이 이 가게가 어떤 곳인 줄 알고 문을 닫아.</x:v>
+        <x:v>뭐? 이 썩을 놈이 이 가게가 어떤 곳인 줄 알고 &lt;shake amp=0.65 hz=18&gt;문을 닫아.&lt;/shake&gt;</x:v>
       </x:c>
       <x:c r="G372" s="18" t="str">
         <x:v>What? That rotten punk — does he even know what this place is, talking about closing it?</x:v>
@@ -37941,7 +37941,7 @@
         <x:v>serious</x:v>
       </x:c>
       <x:c r="F374" s="18" t="str">
-        <x:v>원래 이 바의 주인은 조니라는 친구였지.</x:v>
+        <x:v>원래 이 바의 주인은 &lt;slow&gt;조니라는 친구&lt;/slow&gt;였지.</x:v>
       </x:c>
       <x:c r="G374" s="18" t="str">
         <x:v>The original owner of this bar was a guy named Johnny.</x:v>
@@ -37991,7 +37991,7 @@
         <x:v>serious</x:v>
       </x:c>
       <x:c r="F375" s="18" t="str">
-        <x:v>조니가 있었으면 언노운이 이렇게 되진 않았을 텐데.</x:v>
+        <x:v>조니가 있었으면 언노운이 &lt;wave amp=0.45 hz=1.4 phase=0.6&gt;이렇게 되진 않았을 텐데.&lt;/wave&gt;</x:v>
       </x:c>
       <x:c r="G375" s="18" t="str">
         <x:v>If Johnny were still around, Unknown wouldn't have ended up like this.</x:v>
@@ -38091,7 +38091,7 @@
         <x:v>default</x:v>
       </x:c>
       <x:c r="F377" s="18" t="str">
-        <x:v>그래도 루나 널 보니 뭔가 달라질 수도 있을 것 같네.
+        <x:v>그래도 루나 널 보니 뭔가 &lt;wave amp=0.45 hz=1.4 phase=0.6&gt;달라질 수도 있을 것 같네.&lt;/wave&gt;
 아직 애송이지만 말이야.</x:v>
       </x:c>
       <x:c r="G377" s="18" t="str">
@@ -38897,7 +38897,7 @@
         <x:v>default</x:v>
       </x:c>
       <x:c r="F393" s="18" t="str">
-        <x:v>밖에 나가면 고양이 한 마리가 자고 있을 텐데.
+        <x:v>밖에 나가면 &lt;pop peak=1.11 duration=0.12&gt;고양이 한 마리&lt;/pop&gt;가 자고 있을 텐데.
 데리고 와줘.</x:v>
       </x:c>
       <x:c r="G393" s="18" t="str">
@@ -39051,7 +39051,7 @@
         <x:v>default</x:v>
       </x:c>
       <x:c r="F396" s="18" t="str">
-        <x:v>보수가 충분하다면 못 할 일은 아닙니다.</x:v>
+        <x:v>&lt;pop peak=1.11 duration=0.12&gt;보수가 충분하다면&lt;/pop&gt; 못 할 일은 아닙니다.</x:v>
       </x:c>
       <x:c r="G396" s="18" t="str">
         <x:v>Given sufficient compensation, it is not impossible.</x:v>
@@ -39601,7 +39601,7 @@
         <x:v>joy</x:v>
       </x:c>
       <x:c r="F407" s="18" t="str">
-        <x:v>크크. 오랜만에 제대로 된 작업을 할 수 있겠구먼.</x:v>
+        <x:v>크크. 오랜만에 &lt;slow&gt;제대로 된 작업&lt;/slow&gt;을 할 수 있겠구먼.</x:v>
       </x:c>
       <x:c r="G407" s="18" t="str">
         <x:v>Heh heh. Finally, some proper work after all this time.</x:v>
@@ -52244,7 +52244,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R241b307e9c1747c5"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb914d6cdec8a4bf5"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -52682,7 +52682,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5babcb5a5bff46c0"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3da28fcbdc184fba"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -54286,7 +54286,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8899bf88cd4440db"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R47b3ff897d6b4d7e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -54637,7 +54637,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R93118a37bf10482a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R73d0be374e1249ac"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -56034,7 +56034,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb12baf135d234bb1"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd091399f85dd4bab"/>
   </x:tableParts>
 </x:worksheet>
 </file>